--- a/output/第10期計画_介護給付費分科会の論点整理の受領点検.xlsx
+++ b/output/第10期計画_介護給付費分科会の論点整理の受領点検.xlsx
@@ -79,6 +79,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
@@ -90,11 +95,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DEEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -124,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -143,22 +143,25 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -678,7 +681,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>当方の扱い</t>
+          <t>その後の状況</t>
         </is>
       </c>
     </row>
@@ -698,9 +701,9 @@
           <t>公式議事録の事務局説明により補完</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>計画素案に反映しない</t>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>解消（原典により確認）</t>
         </is>
       </c>
     </row>
@@ -722,7 +725,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>計画素案に反映しない</t>
+          <t>なお確認できていない</t>
         </is>
       </c>
     </row>
@@ -742,16 +745,16 @@
           <t>第257回・第264回等による暫定整理</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>計画素案に反映しない</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="72" customHeight="1">
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>解消（原典により確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="84" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>注1）当方は外部に接続できないため、分科会の資料を直接確認できません。原本のご提供を確認事項No.182 によりお願いしています。
+          <t>注1）本整理の受領の後、別途、分科会の資料11件（全311頁）のご提供を受けました。上表のうち2件はこれにより解消しています。原典による確認は別冊「介護給付費分科会資料（原典）の受領点検」によります。第256回から第267回までの資料はなお受領していないため、これらに係る論点は本整理によるものです（確認事項No.182 は一部解決です）。
 注2）介護給付費分科会は報酬（単位数・加算・基準）を、社会保障審議会介護保険部会は計画・制度を扱う別の審議の場です。本表は両者を区別して整理しています。
 注3）確認基準は2026年10月14日夕方です。これより後に公表された資料は含みません。</t>
         </is>
@@ -788,12 +791,12 @@
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>第256回</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
@@ -803,17 +806,17 @@
           <t>調査と改定の進め方</t>
         </is>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="9" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>第257回</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -823,17 +826,17 @@
           <t>小多機・看多機・認知症GHの一次議論</t>
         </is>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="9" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>第258回</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
@@ -843,17 +846,17 @@
           <t>通所・リハ・短期入所の一次議論</t>
         </is>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="9" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>第259回</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
@@ -863,17 +866,17 @@
           <t>訪問系、ケアマネジメント、福祉用具・住宅改修の一次議論</t>
         </is>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="9" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>第260回</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
@@ -883,17 +886,17 @@
           <t>特養・老健・介護医療院・特定施設</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D24" s="9" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>第261回</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
@@ -903,17 +906,17 @@
           <t>人口減少・需要変化と地域類型に応じた供給確保</t>
         </is>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D25" s="9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>第262回</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
@@ -923,17 +926,17 @@
           <t>定期巡回・夜間対応、住まい、地域区分</t>
         </is>
       </c>
-      <c r="D26" s="8" t="n">
+      <c r="D26" s="9" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>第263回</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
@@ -943,17 +946,17 @@
           <t>人材、処遇、生産性、虐待・安全、BCP、ハラスメント</t>
         </is>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D27" s="9" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>第264回</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
@@ -963,17 +966,17 @@
           <t>認知症、医療連携、LIFE、口腔栄養、室料負担</t>
         </is>
       </c>
-      <c r="D28" s="8" t="n">
+      <c r="D28" s="9" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>第265回</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
@@ -983,17 +986,17 @@
           <t>団体等意見交換①</t>
         </is>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="D29" s="9" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>第266回</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
@@ -1003,17 +1006,17 @@
           <t>団体等意見交換②</t>
         </is>
       </c>
-      <c r="D30" s="8" t="n">
+      <c r="D30" s="9" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>第267回</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
@@ -1023,17 +1026,17 @@
           <t>団体等意見交換③（専門職・過疎離島）</t>
         </is>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="D31" s="9" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>第268回</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
@@ -1043,17 +1046,17 @@
           <t>改定に関する基本的な視点（案）5つの視点</t>
         </is>
       </c>
-      <c r="D32" s="8" t="n">
+      <c r="D32" s="9" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>第269回</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
@@ -1063,17 +1066,17 @@
           <t>定期巡回・小多機・看多機等の具体的対応案</t>
         </is>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="D33" s="9" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>第270回</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
@@ -1083,7 +1086,7 @@
           <t>通所・リハ・短期入所の具体案</t>
         </is>
       </c>
-      <c r="D34" s="8" t="n">
+      <c r="D34" s="9" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1185,7 +1188,7 @@
       </c>
     </row>
     <row r="5" ht="56" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>I01</t>
         </is>
@@ -1215,7 +1218,7 @@
           <t>第1章第9節、第6章第6節2</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>直結</t>
         </is>
@@ -1227,7 +1230,7 @@
       </c>
     </row>
     <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>I02</t>
         </is>
@@ -1257,7 +1260,7 @@
           <t>第2章第6節、第5章 基本目標4</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>関係する</t>
         </is>
@@ -1269,7 +1272,7 @@
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>I03</t>
         </is>
@@ -1299,7 +1302,7 @@
           <t>第1章第9節1、第5章 基本目標4</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>関係する</t>
         </is>
@@ -1311,7 +1314,7 @@
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>I04</t>
         </is>
@@ -1341,7 +1344,7 @@
           <t>第1章第7節、第6章第1節〜第4節</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>直結</t>
         </is>
@@ -1353,7 +1356,7 @@
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>I05</t>
         </is>
@@ -1383,7 +1386,7 @@
           <t>第1章第9節1、第6章第4節1（案D）</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>直結</t>
         </is>
@@ -1395,7 +1398,7 @@
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>I06</t>
         </is>
@@ -1425,7 +1428,7 @@
           <t>第2章第3節、第6章第2節</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>直結</t>
         </is>
@@ -1437,7 +1440,7 @@
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>I07</t>
         </is>
@@ -1467,7 +1470,7 @@
           <t>第6章第2節（2）</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>直結</t>
         </is>
@@ -1479,7 +1482,7 @@
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>I08</t>
         </is>
@@ -1509,7 +1512,7 @@
           <t>第6章第2節（2）</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>関係する</t>
         </is>
@@ -1521,7 +1524,7 @@
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>I09</t>
         </is>
@@ -1551,7 +1554,7 @@
           <t>第6章第2節（2）、第6章第4節1</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>関係する</t>
         </is>
@@ -1563,7 +1566,7 @@
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>I10</t>
         </is>
@@ -1593,7 +1596,7 @@
           <t>第2章第3節、第6章第2節（2）、第6章第4節4</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>直結</t>
         </is>
@@ -1605,7 +1608,7 @@
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>I11</t>
         </is>
@@ -1635,7 +1638,7 @@
           <t>第6章第2節（1）（2）、第6章第4節</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>直結</t>
         </is>
@@ -1647,7 +1650,7 @@
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>I12</t>
         </is>
@@ -1677,7 +1680,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>当区域では扱わない</t>
         </is>
@@ -1689,7 +1692,7 @@
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>I13</t>
         </is>
@@ -1719,7 +1722,7 @@
           <t>第2章第3節5、第6章第2節</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>関係する</t>
         </is>
@@ -1731,7 +1734,7 @@
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>I14</t>
         </is>
@@ -1761,7 +1764,7 @@
           <t>第6章第2節 注1-1、第6章第4節</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>直結</t>
         </is>
@@ -1773,7 +1776,7 @@
       </c>
     </row>
     <row r="19" ht="56" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>I15</t>
         </is>
@@ -1803,7 +1806,7 @@
           <t>第6章第2節、第6章第3節</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>直結</t>
         </is>
@@ -1815,7 +1818,7 @@
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>I16</t>
         </is>
@@ -1845,7 +1848,7 @@
           <t>第5章 基本目標1、第6章第5節</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>関係する</t>
         </is>
@@ -1857,7 +1860,7 @@
       </c>
     </row>
     <row r="21" ht="56" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>I17</t>
         </is>
@@ -1887,7 +1890,7 @@
           <t>第6章第2節（4）居宅介護支援・介護予防支援</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>関係する</t>
         </is>
@@ -1899,7 +1902,7 @@
       </c>
     </row>
     <row r="22" ht="56" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>I18</t>
         </is>
@@ -1929,7 +1932,7 @@
           <t>第5章 基本目標5（3）</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>関係する</t>
         </is>
@@ -1941,7 +1944,7 @@
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>I19</t>
         </is>
@@ -1971,7 +1974,7 @@
           <t>第6章第4節2、第6章第5節</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>直結</t>
         </is>
@@ -1983,7 +1986,7 @@
       </c>
     </row>
     <row r="24" ht="56" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>I20</t>
         </is>
@@ -2013,7 +2016,7 @@
           <t>第6章第5節、第1章第8節</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>直結</t>
         </is>
@@ -2025,7 +2028,7 @@
       </c>
     </row>
     <row r="25" ht="56" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>I21</t>
         </is>
@@ -2055,7 +2058,7 @@
           <t>第2章第3節6、第6章第2節、第6章第4節4</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>直結</t>
         </is>
@@ -2067,7 +2070,7 @@
       </c>
     </row>
     <row r="26" ht="56" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>I22</t>
         </is>
@@ -2097,7 +2100,7 @@
           <t>第1章第2節、第5章 基本目標2（3）</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="12" t="inlineStr">
         <is>
           <t>関係する</t>
         </is>
@@ -2109,7 +2112,7 @@
       </c>
     </row>
     <row r="27" ht="56" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>I23</t>
         </is>
@@ -2139,7 +2142,7 @@
           <t>第1章第9節1、第6章第4節</t>
         </is>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>直結</t>
         </is>
@@ -2151,7 +2154,7 @@
       </c>
     </row>
     <row r="28" ht="56" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>I24</t>
         </is>
@@ -2181,7 +2184,7 @@
           <t>第5章 基本目標1・基本目標3</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>関係する</t>
         </is>
@@ -2193,7 +2196,7 @@
       </c>
     </row>
     <row r="29" ht="56" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>I25</t>
         </is>
@@ -2223,7 +2226,7 @@
           <t>第5章 基本目標1（3）（4）</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>関係する</t>
         </is>
@@ -2235,7 +2238,7 @@
       </c>
     </row>
     <row r="30" ht="56" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>I26</t>
         </is>
@@ -2265,7 +2268,7 @@
           <t>第5章 基本目標5（3）（4）</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>関係する</t>
         </is>
@@ -2277,7 +2280,7 @@
       </c>
     </row>
     <row r="31" ht="56" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>I27</t>
         </is>
@@ -2307,7 +2310,7 @@
           <t>第5章 基本目標4</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>関係する</t>
         </is>
@@ -2319,7 +2322,7 @@
       </c>
     </row>
     <row r="32" ht="56" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>I28</t>
         </is>
@@ -2349,7 +2352,7 @@
           <t>第6章第6節2、第6章第7節</t>
         </is>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>直結</t>
         </is>
@@ -2361,7 +2364,7 @@
       </c>
     </row>
     <row r="33" ht="56" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>I29</t>
         </is>
@@ -2391,7 +2394,7 @@
           <t>第1章第9節1、第1章第8節、第6章第1節〜第3節</t>
         </is>
       </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>直結</t>
         </is>
@@ -2403,7 +2406,7 @@
       </c>
     </row>
     <row r="34" ht="56" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>I30</t>
         </is>
@@ -2433,7 +2436,7 @@
           <t>第1章第9節5、第5章 基本目標1（4）</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>直結</t>
         </is>
@@ -2445,7 +2448,7 @@
       </c>
     </row>
     <row r="35" ht="56" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>I31</t>
         </is>
@@ -2475,7 +2478,7 @@
           <t>第5章 基本目標5、第6章第6節、第6章第7節</t>
         </is>
       </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>直結</t>
         </is>
@@ -2562,7 +2565,7 @@
       </c>
     </row>
     <row r="5" ht="72" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>I01</t>
         </is>
@@ -2590,7 +2593,7 @@
       </c>
     </row>
     <row r="6" ht="72" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>I04</t>
         </is>
@@ -2618,7 +2621,7 @@
       </c>
     </row>
     <row r="7" ht="72" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>I05</t>
         </is>
@@ -2646,7 +2649,7 @@
       </c>
     </row>
     <row r="8" ht="72" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>I06</t>
         </is>
@@ -2674,7 +2677,7 @@
       </c>
     </row>
     <row r="9" ht="72" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>I07</t>
         </is>
@@ -2702,7 +2705,7 @@
       </c>
     </row>
     <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>I10</t>
         </is>
@@ -2730,7 +2733,7 @@
       </c>
     </row>
     <row r="11" ht="72" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>I11</t>
         </is>
@@ -2758,7 +2761,7 @@
       </c>
     </row>
     <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>I14</t>
         </is>
@@ -2786,7 +2789,7 @@
       </c>
     </row>
     <row r="13" ht="72" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>I15</t>
         </is>
@@ -2814,7 +2817,7 @@
       </c>
     </row>
     <row r="14" ht="72" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>I19</t>
         </is>
@@ -2842,7 +2845,7 @@
       </c>
     </row>
     <row r="15" ht="72" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>I20</t>
         </is>
@@ -2870,7 +2873,7 @@
       </c>
     </row>
     <row r="16" ht="72" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>I21</t>
         </is>
@@ -2898,7 +2901,7 @@
       </c>
     </row>
     <row r="17" ht="72" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>I23</t>
         </is>
@@ -2926,7 +2929,7 @@
       </c>
     </row>
     <row r="18" ht="72" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>I28</t>
         </is>
@@ -2954,7 +2957,7 @@
       </c>
     </row>
     <row r="19" ht="72" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>I29</t>
         </is>
@@ -2982,7 +2985,7 @@
       </c>
     </row>
     <row r="20" ht="72" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>I30</t>
         </is>
@@ -3010,7 +3013,7 @@
       </c>
     </row>
     <row r="21" ht="72" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>I31</t>
         </is>
@@ -3080,7 +3083,7 @@
       </c>
     </row>
     <row r="26" ht="64" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>I14</t>
         </is>
@@ -3107,7 +3110,7 @@
       </c>
     </row>
     <row r="27" ht="64" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>I07</t>
         </is>
@@ -3134,7 +3137,7 @@
       </c>
     </row>
     <row r="28" ht="64" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>I21</t>
         </is>
@@ -3161,7 +3164,7 @@
       </c>
     </row>
     <row r="29" ht="64" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>I05</t>
         </is>
@@ -3188,7 +3191,7 @@
       </c>
     </row>
     <row r="30" ht="64" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>I19</t>
         </is>
@@ -3290,7 +3293,7 @@
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>量（利用者数）</t>
         </is>
@@ -3317,7 +3320,7 @@
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>量（区分）</t>
         </is>
@@ -3344,7 +3347,7 @@
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>量（回・日数）</t>
         </is>
@@ -3371,7 +3374,7 @@
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>単価</t>
         </is>
@@ -3398,7 +3401,7 @@
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>制度・負担</t>
         </is>
@@ -3519,7 +3522,7 @@
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>令和8年12月頃</t>
         </is>
@@ -3541,7 +3544,7 @@
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>令和9年1月頃</t>
         </is>
@@ -3875,7 +3878,7 @@
       </c>
     </row>
     <row r="5" ht="56" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>P01</t>
         </is>
@@ -3890,7 +3893,7 @@
           <t>I04・I29</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>実施済み（一部）</t>
         </is>
@@ -3902,7 +3905,7 @@
       </c>
     </row>
     <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>P02</t>
         </is>
@@ -3917,7 +3920,7 @@
           <t>I05・I06・I11〜I16</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>一部実施</t>
         </is>
@@ -3929,7 +3932,7 @@
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>P03</t>
         </is>
@@ -3944,7 +3947,7 @@
           <t>I07〜I09</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>一部実施</t>
         </is>
@@ -3956,7 +3959,7 @@
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>P04</t>
         </is>
@@ -3971,7 +3974,7 @@
           <t>I19〜I21</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>一部実施</t>
         </is>
@@ -3983,7 +3986,7 @@
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>P05</t>
         </is>
@@ -3998,7 +4001,7 @@
           <t>I02・I03・I17・I27</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>一部実施</t>
         </is>
@@ -4010,7 +4013,7 @@
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>P06</t>
         </is>
@@ -4025,7 +4028,7 @@
           <t>I09・I16・I20・I23</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>一部実施</t>
         </is>
@@ -4037,7 +4040,7 @@
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>P07</t>
         </is>
@@ -4052,7 +4055,7 @@
           <t>I10・I22・I25</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>決定待ち</t>
         </is>
@@ -4064,7 +4067,7 @@
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>P08</t>
         </is>
@@ -4079,7 +4082,7 @@
           <t>I18・I24〜I26</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>一部実施</t>
         </is>
@@ -4091,7 +4094,7 @@
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>P09</t>
         </is>
@@ -4106,7 +4109,7 @@
           <t>I30</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>決定待ち</t>
         </is>
@@ -4118,7 +4121,7 @@
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
@@ -4133,7 +4136,7 @@
           <t>I01・I28・I31</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>実施済み</t>
         </is>
@@ -4220,7 +4223,7 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="9" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -4228,7 +4231,7 @@
           <t>1人あたり給付費（単価）</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -4245,7 +4248,7 @@
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="9" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -4253,7 +4256,7 @@
           <t>要介護度別の単価</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
@@ -4270,7 +4273,7 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="9" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -4278,7 +4281,7 @@
           <t>1人1月あたり利用回（日）数</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
@@ -4295,7 +4298,7 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="9" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -4303,7 +4306,7 @@
           <t>要介護度の構成</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
@@ -4320,7 +4323,7 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="9" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -4328,7 +4331,7 @@
           <t>地域支援事業費（B）</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4345,7 +4348,7 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="9" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -4353,7 +4356,7 @@
           <t>総合事業費</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4370,7 +4373,7 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="9" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -4378,7 +4381,7 @@
           <t>総合事業の量の見込み</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4395,7 +4398,7 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="9" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -4403,7 +4406,7 @@
           <t>必要利用定員総数</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4420,7 +4423,7 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="9" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -4428,7 +4431,7 @@
           <t>認知症対応型共同生活介護の定員</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4445,7 +4448,7 @@
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="9" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -4453,7 +4456,7 @@
           <t>施設・居住系の定員の縮小</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4470,7 +4473,7 @@
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="9" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -4478,7 +4481,7 @@
           <t>対計画比の偏りの補正</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4495,7 +4498,7 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="9" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -4503,7 +4506,7 @@
           <t>季節補正</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
@@ -4520,7 +4523,7 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="9" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -4528,7 +4531,7 @@
           <t>施策の反映</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4545,7 +4548,7 @@
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="9" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -4553,7 +4556,7 @@
           <t>給付適正化による抑制</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4570,7 +4573,7 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="9" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -4578,7 +4581,7 @@
           <t>第1号被保険者負担割合</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -4595,7 +4598,7 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="9" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -4603,7 +4606,7 @@
           <t>予定保険料収納率</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4620,7 +4623,7 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="9" t="n">
         <v>17</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -4628,7 +4631,7 @@
           <t>基金の取崩し</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4645,7 +4648,7 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="9" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -4653,7 +4656,7 @@
           <t>所得段階別加入割合補正</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -4670,7 +4673,7 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="9" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -4678,7 +4681,7 @@
           <t>令和9年4月新設のサービス区分</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -4695,7 +4698,7 @@
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="9" t="n">
         <v>20</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -4703,7 +4706,7 @@
           <t>混合型特定施設の必要利用定員総数</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4720,7 +4723,7 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="8" t="n">
+      <c r="A25" s="9" t="n">
         <v>21</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -4728,7 +4731,7 @@
           <t>供給の制約（定員上限）</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4745,7 +4748,7 @@
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="9" t="n">
         <v>22</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -4753,7 +4756,7 @@
           <t>供給の制約（人材・受入可能量）</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4770,7 +4773,7 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="8" t="n">
+      <c r="A27" s="9" t="n">
         <v>23</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -4778,7 +4781,7 @@
           <t>施設に入れない方の在宅サービスの使い方</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4870,7 +4873,7 @@
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>I05</t>
         </is>
@@ -4892,7 +4895,7 @@
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>I07</t>
         </is>
@@ -4914,7 +4917,7 @@
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>I14</t>
         </is>
@@ -4936,7 +4939,7 @@
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>I21</t>
         </is>
@@ -4958,7 +4961,7 @@
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>I28</t>
         </is>
@@ -4980,7 +4983,7 @@
       </c>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>I01</t>
         </is>
@@ -5040,7 +5043,7 @@
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="12" t="n">
         <v>182</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -5060,7 +5063,7 @@
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="11" t="n">
+      <c r="A17" s="12" t="n">
         <v>183</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -5080,7 +5083,7 @@
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="12" t="n">
         <v>184</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -5177,7 +5180,7 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="9" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -5195,14 +5198,14 @@
           <t>31件</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="9" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -5220,14 +5223,14 @@
           <t>欠番0件・重複0件</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="9" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -5245,14 +5248,14 @@
           <t>31／31件</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="9" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -5270,14 +5273,14 @@
           <t>17件</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="9" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -5295,14 +5298,14 @@
           <t>15回（第256回〜第270回）</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="9" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -5320,14 +5323,14 @@
           <t>3件</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="9" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -5345,14 +5348,14 @@
           <t>記載あり</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="9" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -5370,14 +5373,14 @@
           <t>素案にない章節 0件</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="9" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -5395,14 +5398,14 @@
           <t>第5章、第1章第9節、第2章第2節、第2章第3節、第2章第5節、第4章第3節、第6章第2節、第6章第4節</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="9" t="n">
         <v>9.1</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -5420,14 +5423,14 @@
           <t>第1章第9節、第6章第2節</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -5445,14 +5448,14 @@
           <t>第1章第9節、第2章第3節、第6章第6節</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="9" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -5470,14 +5473,14 @@
           <t>第1章第9節、第6章第3節</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="9" t="n">
         <v>9.4</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -5495,14 +5498,14 @@
           <t>第5章、第1章第9節、第6章第2節、第6章第4節、第6章第7節</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="9" t="n">
         <v>10</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -5520,14 +5523,14 @@
           <t>3／3件</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="9" t="n">
         <v>11</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -5545,14 +5548,14 @@
           <t>3／3件</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="9" t="n">
         <v>12</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -5570,14 +5573,14 @@
           <t>3／3件</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="9" t="n">
         <v>13</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -5595,14 +5598,14 @@
           <t>区分C 4件</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="9" t="n">
         <v>14</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -5620,14 +5623,14 @@
           <t>現れない</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="9" t="n">
         <v>15</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -5645,14 +5648,14 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="9" t="n">
         <v>16</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -5670,7 +5673,7 @@
           <t>現れない</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>

--- a/output/第10期計画_介護給付費分科会の論点整理の受領点検.xlsx
+++ b/output/第10期計画_介護給付費分科会の論点整理の受領点検.xlsx
@@ -754,7 +754,7 @@
     <row r="16" ht="84" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>注1）本整理の受領の後、別途、分科会の資料11件（全311頁）のご提供を受けました。上表のうち2件はこれにより解消しています。原典による確認は別冊「介護給付費分科会資料（原典）の受領点検」によります。第256回から第267回までの資料はなお受領していないため、これらに係る論点は本整理によるものです（確認事項No.182 は一部解決です）。
+          <t>注1）本整理の受領の後、別途、分科会の資料25件（全1037頁）のご提供を受けました。上表のうち2件はこれにより解消しています。原典による確認は別冊「介護給付費分科会資料（原典）の受領点検」によります。第256回から第267回までの資料はなお受領していないため、これらに係る論点は本整理によるものです（確認事項No.182 は一部解決です）。
 注2）介護給付費分科会は報酬（単位数・加算・基準）を、社会保障審議会介護保険部会は計画・制度を扱う別の審議の場です。本表は両者を区別して整理しています。
 注3）確認基準は2026年10月14日夕方です。これより後に公表された資料は含みません。</t>
         </is>

--- a/output/第10期計画_介護給付費分科会の論点整理の受領点検.xlsx
+++ b/output/第10期計画_介護給付費分科会の論点整理の受領点検.xlsx
@@ -5495,7 +5495,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>第5章、第1章第9節、第6章第2節、第6章第4節、第6章第7節</t>
+          <t>第5章、第1章第9節、第6章第2節、第6章第3節、第6章第4節、第6章第7節</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">

--- a/output/第10期計画_介護給付費分科会の論点整理の受領点検.xlsx
+++ b/output/第10期計画_介護給付費分科会の論点整理の受領点検.xlsx
@@ -1771,7 +1771,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>短期入所生活介護の見込量を立てている。**積雪期の季節利用に係る例外は当区域に直接関わる**</t>
+          <t>短期入所生活介護の見込量を立てている。積雪期の季節利用に係る例外は当区域に直接関わる</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>介護保険の指定を受けない住まい339人・戸を把握している。**同一建物減算に代わる報酬区分の見直しは単価に及ぶ**</t>
+          <t>介護保険の指定を受けない住まい339人・戸を把握している。同一建物減算に代わる報酬区分の見直しは単価に及ぶ</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       <c r="D12" s="5" t="inlineStr">
         <is>
           <t>第6章第2節 注1-1、第6章第4節
-短期入所生活介護の見込量を立てている。**積雪期の季節利用に係る例外は当区域に直接関わる**</t>
+短期入所生活介護の見込量を立てている。積雪期の季節利用に係る例外は当区域に直接関わる</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -2891,7 +2891,7 @@
       <c r="D16" s="5" t="inlineStr">
         <is>
           <t>第2章第3節6、第6章第2節、第6章第4節4
-介護保険の指定を受けない住まい339人・戸を把握している。**同一建物減算に代わる報酬区分の見直しは単価に及ぶ**</t>
+介護保険の指定を受けない住まい339人・戸を把握している。同一建物減算に代わる報酬区分の見直しは単価に及ぶ</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
